--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4716784bbc33fc8c/바탕 화면/앱 관련/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBE2D0DE-DFD8-417C-9C99-BDED21FD0092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D6AD43F-F395-4691-843B-740155F5A6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{524E4321-34C6-4851-BBC3-552957EB36E1}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{524E4321-34C6-4851-BBC3-552957EB36E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="420">
   <si>
     <t>SPFH590 2.0*148</t>
   </si>
@@ -1103,9 +1103,6 @@
     <t>(8HP50 TURBINE SHELL)</t>
   </si>
   <si>
-    <t>(2-1, 5-7, PRA, PRB T/S) 대운테</t>
-  </si>
-  <si>
     <t>(KDE JH TURBINE)</t>
   </si>
   <si>
@@ -1269,13 +1266,40 @@
   </si>
   <si>
     <t>SAE1050SHX</t>
+  </si>
+  <si>
+    <t>(2-1, 5-7, PRA, PRB T/S)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SPHC-P</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PULLEY 0697</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SPHD</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GE000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GT000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="180" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1297,6 +1321,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -1366,7 +1398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1380,6 +1412,8 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1684,7 +1718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6849FD11-1D35-422D-825C-843B8DFC35E0}">
-  <dimension ref="A1:D216"/>
+  <dimension ref="A1:E219"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="7.5" bestFit="1" customWidth="1"/>
@@ -3597,8 +3631,8 @@
       <c r="C152">
         <v>542</v>
       </c>
-      <c r="D152" t="s">
-        <v>359</v>
+      <c r="D152" s="5" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
@@ -3612,7 +3646,7 @@
         <v>581</v>
       </c>
       <c r="D153" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
@@ -3637,7 +3671,7 @@
         <v>305</v>
       </c>
       <c r="D155" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
@@ -3651,7 +3685,7 @@
         <v>550</v>
       </c>
       <c r="D156" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
@@ -3665,7 +3699,7 @@
         <v>540</v>
       </c>
       <c r="D157" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
@@ -3690,7 +3724,7 @@
         <v>120</v>
       </c>
       <c r="D159" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
@@ -3715,7 +3749,7 @@
         <v>230</v>
       </c>
       <c r="D161" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
@@ -3740,7 +3774,7 @@
         <v>118</v>
       </c>
       <c r="D163" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
@@ -3787,7 +3821,7 @@
         <v>150</v>
       </c>
       <c r="D167" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
@@ -3812,7 +3846,7 @@
         <v>170</v>
       </c>
       <c r="D169" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
@@ -3826,7 +3860,7 @@
         <v>175</v>
       </c>
       <c r="D170" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
@@ -3851,12 +3885,12 @@
         <v>680</v>
       </c>
       <c r="D172" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B173">
         <v>1.8</v>
@@ -3867,7 +3901,7 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B174">
         <v>1.8</v>
@@ -3876,12 +3910,12 @@
         <v>335</v>
       </c>
       <c r="D174" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B175">
         <v>0.5</v>
@@ -3890,12 +3924,12 @@
         <v>156</v>
       </c>
       <c r="D175" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B176">
         <v>2</v>
@@ -3906,7 +3940,7 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B177">
         <v>2</v>
@@ -3917,7 +3951,7 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B178">
         <v>2.5</v>
@@ -3926,12 +3960,12 @@
         <v>1219</v>
       </c>
       <c r="D178" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -3942,7 +3976,7 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -3953,7 +3987,7 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B181">
         <v>0.6</v>
@@ -3962,12 +3996,12 @@
         <v>60</v>
       </c>
       <c r="D181" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B182">
         <v>3</v>
@@ -3976,12 +4010,12 @@
         <v>168</v>
       </c>
       <c r="D182" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B183">
         <v>3</v>
@@ -3990,12 +4024,12 @@
         <v>1000</v>
       </c>
       <c r="D183" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B184">
         <v>6</v>
@@ -4009,7 +4043,7 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B185">
         <v>0.6</v>
@@ -4020,7 +4054,7 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -4031,7 +4065,7 @@
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B187">
         <v>1.5</v>
@@ -4042,7 +4076,7 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B188">
         <v>1.5</v>
@@ -4051,12 +4085,12 @@
         <v>68</v>
       </c>
       <c r="D188" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B189">
         <v>2</v>
@@ -4065,12 +4099,12 @@
         <v>50</v>
       </c>
       <c r="D189" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B190">
         <v>2</v>
@@ -4079,12 +4113,12 @@
         <v>81</v>
       </c>
       <c r="D190" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B191">
         <v>2</v>
@@ -4095,7 +4129,7 @@
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B192">
         <v>2</v>
@@ -4106,7 +4140,7 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B193">
         <v>2</v>
@@ -4117,7 +4151,7 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B194">
         <v>2</v>
@@ -4128,7 +4162,7 @@
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B195">
         <v>2</v>
@@ -4137,12 +4171,12 @@
         <v>180</v>
       </c>
       <c r="D195" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B196">
         <v>0.8</v>
@@ -4151,12 +4185,12 @@
         <v>48</v>
       </c>
       <c r="D196" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -4167,7 +4201,7 @@
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -4178,7 +4212,7 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B199">
         <v>1.7</v>
@@ -4189,7 +4223,7 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B200">
         <v>1.8</v>
@@ -4198,12 +4232,12 @@
         <v>202</v>
       </c>
       <c r="D200" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B201">
         <v>1.8</v>
@@ -4212,12 +4246,12 @@
         <v>225</v>
       </c>
       <c r="D201" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B202">
         <v>1.8</v>
@@ -4226,12 +4260,12 @@
         <v>335</v>
       </c>
       <c r="D202" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B203">
         <v>1.8</v>
@@ -4240,138 +4274,181 @@
         <v>335</v>
       </c>
       <c r="D203" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
+        <v>398</v>
+      </c>
+      <c r="B204" s="6">
+        <v>5.9</v>
+      </c>
+      <c r="D204" t="s">
         <v>399</v>
-      </c>
-      <c r="B204">
-        <v>5.9</v>
-      </c>
-      <c r="D204" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>399</v>
-      </c>
-      <c r="B205">
+        <v>398</v>
+      </c>
+      <c r="B205" s="6">
         <v>6</v>
       </c>
       <c r="D205" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>399</v>
-      </c>
-      <c r="B206">
+        <v>398</v>
+      </c>
+      <c r="B206" s="6">
         <v>6.9</v>
       </c>
       <c r="D206" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>399</v>
-      </c>
-      <c r="B207">
+        <v>398</v>
+      </c>
+      <c r="B207" s="6">
         <v>7</v>
       </c>
       <c r="D207" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>399</v>
-      </c>
-      <c r="B208">
+        <v>398</v>
+      </c>
+      <c r="B208" s="6">
         <v>7.35</v>
       </c>
       <c r="D208" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>398</v>
+      </c>
+      <c r="B209" s="6">
+        <v>7.45</v>
+      </c>
+      <c r="D209" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A209" t="s">
-        <v>399</v>
-      </c>
-      <c r="B209">
-        <v>7.45</v>
-      </c>
-      <c r="D209" t="s">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>398</v>
+      </c>
+      <c r="B210" s="6">
+        <v>8</v>
+      </c>
+      <c r="D210" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A210" t="s">
-        <v>399</v>
-      </c>
-      <c r="B210">
-        <v>8</v>
-      </c>
-      <c r="D210" t="s">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A211" t="s">
+      <c r="B211" s="6">
+        <v>6</v>
+      </c>
+      <c r="D211" t="s">
         <v>407</v>
       </c>
-      <c r="B211">
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>408</v>
+      </c>
+      <c r="B212" s="6">
+        <v>7.35</v>
+      </c>
+      <c r="D212" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>410</v>
+      </c>
+      <c r="B213" s="6">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>411</v>
+      </c>
+      <c r="B214" s="6">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>412</v>
+      </c>
+      <c r="B215" s="6">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>413</v>
+      </c>
+      <c r="B216" s="6">
         <v>6</v>
       </c>
-      <c r="D211" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A212" t="s">
-        <v>409</v>
-      </c>
-      <c r="B212">
-        <v>7.35</v>
-      </c>
-      <c r="D212" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A213" t="s">
-        <v>411</v>
-      </c>
-      <c r="B213">
-        <v>7.9</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A214" t="s">
-        <v>412</v>
-      </c>
-      <c r="B214">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A215" t="s">
-        <v>413</v>
-      </c>
-      <c r="B215">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A216" t="s">
-        <v>414</v>
-      </c>
-      <c r="B216">
-        <v>6</v>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A217" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="B217" s="6">
+        <v>5</v>
+      </c>
+      <c r="C217">
+        <v>394</v>
+      </c>
+      <c r="D217" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="E217" s="5"/>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A218" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="B218" s="6">
+        <v>4.5</v>
+      </c>
+      <c r="C218">
+        <v>174</v>
+      </c>
+      <c r="D218" s="5" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A219" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="B219" s="6">
+        <v>4.5</v>
+      </c>
+      <c r="C219">
+        <v>226</v>
+      </c>
+      <c r="D219" s="5" t="s">
+        <v>419</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4716784bbc33fc8c/바탕 화면/앱 관련/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D6AD43F-F395-4691-843B-740155F5A6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{8D6AD43F-F395-4691-843B-740155F5A6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCF19CE5-8C0A-49D1-A50B-BB5B2369E01B}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{524E4321-34C6-4851-BBC3-552957EB36E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{524E4321-34C6-4851-BBC3-552957EB36E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="420">
   <si>
     <t>SPFH590 2.0*148</t>
   </si>
@@ -1215,9 +1215,6 @@
   </si>
   <si>
     <t>(NEM / NGM 포스맥)</t>
-  </si>
-  <si>
-    <t>(원가용)</t>
   </si>
   <si>
     <t>SCM435</t>
@@ -1289,6 +1286,10 @@
   </si>
   <si>
     <t>GT000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>제품 단중</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1297,7 +1298,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="180" formatCode="0.0"/>
+    <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -1413,7 +1414,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1718,15 +1719,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6849FD11-1D35-422D-825C-843B8DFC35E0}">
-  <dimension ref="A1:E219"/>
+  <dimension ref="A1:F216"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="7.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>256</v>
       </c>
@@ -1736,11 +1738,14 @@
       <c r="C1" t="s">
         <v>258</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="E1" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>259</v>
       </c>
@@ -1751,7 +1756,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>259</v>
       </c>
@@ -1761,11 +1766,14 @@
       <c r="C3">
         <v>212</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3">
+        <v>0.17219999999999999</v>
+      </c>
+      <c r="E3" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>259</v>
       </c>
@@ -1775,11 +1783,14 @@
       <c r="C4">
         <v>272</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4">
+        <v>0.19570000000000001</v>
+      </c>
+      <c r="E4" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>259</v>
       </c>
@@ -1790,7 +1801,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>259</v>
       </c>
@@ -1801,7 +1812,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>259</v>
       </c>
@@ -1811,11 +1822,14 @@
       <c r="C7">
         <v>281</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7">
+        <v>0.22850000000000001</v>
+      </c>
+      <c r="E7" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>259</v>
       </c>
@@ -1826,7 +1840,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>259</v>
       </c>
@@ -1836,11 +1850,14 @@
       <c r="C9">
         <v>238</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9">
+        <v>0.1361</v>
+      </c>
+      <c r="E9" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>259</v>
       </c>
@@ -1850,11 +1867,11 @@
       <c r="C10">
         <v>160</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>259</v>
       </c>
@@ -1864,11 +1881,11 @@
       <c r="C11">
         <v>190</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>266</v>
       </c>
@@ -1879,7 +1896,7 @@
         <v>119.8</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>266</v>
       </c>
@@ -1890,7 +1907,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>266</v>
       </c>
@@ -1901,7 +1918,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>266</v>
       </c>
@@ -1912,7 +1929,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>266</v>
       </c>
@@ -1923,7 +1940,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>266</v>
       </c>
@@ -1934,7 +1951,7 @@
         <v>144.5</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>266</v>
       </c>
@@ -1944,11 +1961,14 @@
       <c r="C18">
         <v>238</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18">
+        <v>0.21099999999999999</v>
+      </c>
+      <c r="E18" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>266</v>
       </c>
@@ -1959,7 +1979,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>266</v>
       </c>
@@ -1970,7 +1990,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>266</v>
       </c>
@@ -1980,11 +2000,14 @@
       <c r="C21">
         <v>251</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21">
+        <v>0.2359</v>
+      </c>
+      <c r="E21" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>266</v>
       </c>
@@ -1994,11 +2017,14 @@
       <c r="C22">
         <v>256</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22">
+        <v>0.24510000000000001</v>
+      </c>
+      <c r="E22" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>266</v>
       </c>
@@ -2009,7 +2035,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>266</v>
       </c>
@@ -2019,11 +2045,11 @@
       <c r="C24">
         <v>270</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>266</v>
       </c>
@@ -2034,7 +2060,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>266</v>
       </c>
@@ -2045,7 +2071,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>266</v>
       </c>
@@ -2055,11 +2081,11 @@
       <c r="C27">
         <v>204</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>266</v>
       </c>
@@ -2069,11 +2095,11 @@
       <c r="C28">
         <v>77</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>266</v>
       </c>
@@ -2083,11 +2109,14 @@
       <c r="C29">
         <v>179</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29">
+        <v>0.1394</v>
+      </c>
+      <c r="E29" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>266</v>
       </c>
@@ -2097,11 +2126,14 @@
       <c r="C30">
         <v>192</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30">
+        <v>0.16059999999999999</v>
+      </c>
+      <c r="E30" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>266</v>
       </c>
@@ -2112,7 +2144,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>266</v>
       </c>
@@ -2122,11 +2154,11 @@
       <c r="C32">
         <v>204</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>266</v>
       </c>
@@ -2136,11 +2168,11 @@
       <c r="C33">
         <v>170</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>266</v>
       </c>
@@ -2151,7 +2183,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>266</v>
       </c>
@@ -2161,11 +2193,11 @@
       <c r="C35">
         <v>335</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>266</v>
       </c>
@@ -2175,11 +2207,11 @@
       <c r="C36">
         <v>108</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>266</v>
       </c>
@@ -2189,11 +2221,11 @@
       <c r="C37">
         <v>589</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>266</v>
       </c>
@@ -2203,11 +2235,11 @@
       <c r="C38">
         <v>108</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>266</v>
       </c>
@@ -2217,11 +2249,11 @@
       <c r="C39">
         <v>164</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>266</v>
       </c>
@@ -2232,7 +2264,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>282</v>
       </c>
@@ -2243,7 +2275,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>284</v>
       </c>
@@ -2254,7 +2286,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>285</v>
       </c>
@@ -2264,11 +2296,11 @@
       <c r="C43">
         <v>103</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>285</v>
       </c>
@@ -2278,11 +2310,11 @@
       <c r="C44">
         <v>116</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>285</v>
       </c>
@@ -2292,11 +2324,11 @@
       <c r="C45">
         <v>119</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>284</v>
       </c>
@@ -2307,7 +2339,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>289</v>
       </c>
@@ -2317,11 +2349,11 @@
       <c r="C47">
         <v>70.400000000000006</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>289</v>
       </c>
@@ -2332,7 +2364,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>291</v>
       </c>
@@ -2343,7 +2375,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>292</v>
       </c>
@@ -2354,7 +2386,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>293</v>
       </c>
@@ -2365,7 +2397,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>294</v>
       </c>
@@ -2375,11 +2407,11 @@
       <c r="C52">
         <v>170</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>294</v>
       </c>
@@ -2390,7 +2422,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>294</v>
       </c>
@@ -2401,7 +2433,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>294</v>
       </c>
@@ -2412,7 +2444,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>296</v>
       </c>
@@ -2422,11 +2454,11 @@
       <c r="C56">
         <v>413</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>298</v>
       </c>
@@ -2437,7 +2469,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>296</v>
       </c>
@@ -2448,7 +2480,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>296</v>
       </c>
@@ -2458,11 +2490,11 @@
       <c r="C59">
         <v>520</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>296</v>
       </c>
@@ -2473,7 +2505,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>296</v>
       </c>
@@ -2483,11 +2515,11 @@
       <c r="C61">
         <v>334</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>296</v>
       </c>
@@ -2497,11 +2529,11 @@
       <c r="C62">
         <v>500</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>296</v>
       </c>
@@ -2511,11 +2543,11 @@
       <c r="C63">
         <v>503</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>296</v>
       </c>
@@ -2525,11 +2557,11 @@
       <c r="C64">
         <v>512</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>296</v>
       </c>
@@ -2540,7 +2572,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>296</v>
       </c>
@@ -2551,7 +2583,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>296</v>
       </c>
@@ -2561,11 +2593,11 @@
       <c r="C67">
         <v>537</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>296</v>
       </c>
@@ -2575,11 +2607,11 @@
       <c r="C68">
         <v>514</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>296</v>
       </c>
@@ -2589,11 +2621,11 @@
       <c r="C69">
         <v>520</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>296</v>
       </c>
@@ -2603,11 +2635,11 @@
       <c r="C70">
         <v>529</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>296</v>
       </c>
@@ -2617,11 +2649,11 @@
       <c r="C71">
         <v>160</v>
       </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>296</v>
       </c>
@@ -2631,11 +2663,11 @@
       <c r="C72">
         <v>210</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>296</v>
       </c>
@@ -2646,7 +2678,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>296</v>
       </c>
@@ -2656,11 +2688,11 @@
       <c r="C74">
         <v>495</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>296</v>
       </c>
@@ -2671,7 +2703,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>296</v>
       </c>
@@ -2682,7 +2714,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>296</v>
       </c>
@@ -2692,11 +2724,11 @@
       <c r="C77">
         <v>392</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>296</v>
       </c>
@@ -2706,11 +2738,11 @@
       <c r="C78">
         <v>641</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>296</v>
       </c>
@@ -2721,7 +2753,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>296</v>
       </c>
@@ -2731,11 +2763,11 @@
       <c r="C80">
         <v>195</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>296</v>
       </c>
@@ -2745,11 +2777,11 @@
       <c r="C81">
         <v>525</v>
       </c>
-      <c r="D81" t="s">
+      <c r="E81" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>296</v>
       </c>
@@ -2759,11 +2791,11 @@
       <c r="C82">
         <v>106</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>296</v>
       </c>
@@ -2773,11 +2805,11 @@
       <c r="C83">
         <v>514</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>296</v>
       </c>
@@ -2787,11 +2819,11 @@
       <c r="C84">
         <v>153</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>296</v>
       </c>
@@ -2802,7 +2834,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>296</v>
       </c>
@@ -2813,7 +2845,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>296</v>
       </c>
@@ -2824,7 +2856,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>296</v>
       </c>
@@ -2834,11 +2866,11 @@
       <c r="C88">
         <v>382</v>
       </c>
-      <c r="D88" t="s">
+      <c r="E88" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>296</v>
       </c>
@@ -2848,11 +2880,11 @@
       <c r="C89">
         <v>585</v>
       </c>
-      <c r="D89" t="s">
+      <c r="E89" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>296</v>
       </c>
@@ -2863,7 +2895,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>296</v>
       </c>
@@ -2873,11 +2905,11 @@
       <c r="C91">
         <v>590</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>296</v>
       </c>
@@ -2887,11 +2919,11 @@
       <c r="C92">
         <v>602</v>
       </c>
-      <c r="D92" t="s">
+      <c r="E92" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>296</v>
       </c>
@@ -2901,11 +2933,11 @@
       <c r="C93">
         <v>654</v>
       </c>
-      <c r="D93" t="s">
+      <c r="E93" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>323</v>
       </c>
@@ -2916,7 +2948,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>323</v>
       </c>
@@ -2927,7 +2959,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>324</v>
       </c>
@@ -2938,7 +2970,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>324</v>
       </c>
@@ -2949,7 +2981,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>324</v>
       </c>
@@ -2960,7 +2992,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>325</v>
       </c>
@@ -2971,7 +3003,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>325</v>
       </c>
@@ -2981,11 +3013,11 @@
       <c r="C100">
         <v>508</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>325</v>
       </c>
@@ -2995,11 +3027,11 @@
       <c r="C101">
         <v>530</v>
       </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>325</v>
       </c>
@@ -3009,11 +3041,11 @@
       <c r="C102">
         <v>508</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>329</v>
       </c>
@@ -3023,11 +3055,11 @@
       <c r="C103">
         <v>96</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>331</v>
       </c>
@@ -3037,11 +3069,11 @@
       <c r="C104">
         <v>186</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>331</v>
       </c>
@@ -3051,11 +3083,11 @@
       <c r="C105">
         <v>1230</v>
       </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>331</v>
       </c>
@@ -3066,7 +3098,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>334</v>
       </c>
@@ -3077,7 +3109,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>334</v>
       </c>
@@ -3088,7 +3120,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>334</v>
       </c>
@@ -3099,7 +3131,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>334</v>
       </c>
@@ -3110,7 +3142,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>334</v>
       </c>
@@ -3121,7 +3153,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>334</v>
       </c>
@@ -3132,7 +3164,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>334</v>
       </c>
@@ -3143,7 +3175,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>334</v>
       </c>
@@ -3154,7 +3186,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>334</v>
       </c>
@@ -3164,11 +3196,11 @@
       <c r="C115">
         <v>65</v>
       </c>
-      <c r="D115" t="s">
+      <c r="E115" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>334</v>
       </c>
@@ -3178,11 +3210,11 @@
       <c r="C116">
         <v>165</v>
       </c>
-      <c r="D116" t="s">
+      <c r="E116" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>334</v>
       </c>
@@ -3192,11 +3224,11 @@
       <c r="C117">
         <v>184</v>
       </c>
-      <c r="D117" t="s">
+      <c r="E117" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>334</v>
       </c>
@@ -3207,7 +3239,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>334</v>
       </c>
@@ -3218,7 +3250,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>334</v>
       </c>
@@ -3229,7 +3261,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>334</v>
       </c>
@@ -3240,7 +3272,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>334</v>
       </c>
@@ -3251,7 +3283,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>334</v>
       </c>
@@ -3262,7 +3294,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>334</v>
       </c>
@@ -3272,11 +3304,11 @@
       <c r="C124">
         <v>336</v>
       </c>
-      <c r="D124" t="s">
+      <c r="E124" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>334</v>
       </c>
@@ -3287,7 +3319,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>334</v>
       </c>
@@ -3298,7 +3330,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>334</v>
       </c>
@@ -3308,11 +3340,11 @@
       <c r="C127">
         <v>69</v>
       </c>
-      <c r="D127" t="s">
+      <c r="E127" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>334</v>
       </c>
@@ -3322,11 +3354,11 @@
       <c r="C128">
         <v>117</v>
       </c>
-      <c r="D128" t="s">
+      <c r="E128" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>334</v>
       </c>
@@ -3336,11 +3368,11 @@
       <c r="C129">
         <v>1219</v>
       </c>
-      <c r="D129" t="s">
+      <c r="E129" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>334</v>
       </c>
@@ -3351,7 +3383,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>334</v>
       </c>
@@ -3361,11 +3393,11 @@
       <c r="C131">
         <v>48</v>
       </c>
-      <c r="D131" t="s">
+      <c r="E131" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>334</v>
       </c>
@@ -3375,11 +3407,11 @@
       <c r="C132">
         <v>52</v>
       </c>
-      <c r="D132" t="s">
+      <c r="E132" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>344</v>
       </c>
@@ -3390,7 +3422,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>344</v>
       </c>
@@ -3401,7 +3433,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>345</v>
       </c>
@@ -3412,7 +3444,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>345</v>
       </c>
@@ -3423,7 +3455,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>346</v>
       </c>
@@ -3434,7 +3466,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>346</v>
       </c>
@@ -3445,7 +3477,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>346</v>
       </c>
@@ -3455,11 +3487,11 @@
       <c r="C139">
         <v>113</v>
       </c>
-      <c r="D139" t="s">
+      <c r="E139" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>346</v>
       </c>
@@ -3469,11 +3501,11 @@
       <c r="C140">
         <v>123</v>
       </c>
-      <c r="D140" t="s">
+      <c r="E140" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>346</v>
       </c>
@@ -3483,11 +3515,11 @@
       <c r="C141">
         <v>131</v>
       </c>
-      <c r="D141" t="s">
+      <c r="E141" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>346</v>
       </c>
@@ -3497,11 +3529,11 @@
       <c r="C142">
         <v>180</v>
       </c>
-      <c r="D142" t="s">
+      <c r="E142" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>346</v>
       </c>
@@ -3511,11 +3543,11 @@
       <c r="C143">
         <v>223.5</v>
       </c>
-      <c r="D143" t="s">
+      <c r="E143" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>346</v>
       </c>
@@ -3525,11 +3557,11 @@
       <c r="C144">
         <v>59</v>
       </c>
-      <c r="D144" t="s">
+      <c r="E144" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>346</v>
       </c>
@@ -3540,7 +3572,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>346</v>
       </c>
@@ -3550,11 +3582,11 @@
       <c r="C146">
         <v>164</v>
       </c>
-      <c r="D146" t="s">
+      <c r="E146" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>346</v>
       </c>
@@ -3564,11 +3596,11 @@
       <c r="C147">
         <v>202</v>
       </c>
-      <c r="D147" t="s">
+      <c r="E147" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>355</v>
       </c>
@@ -3579,7 +3611,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>355</v>
       </c>
@@ -3589,11 +3621,11 @@
       <c r="C149">
         <v>324</v>
       </c>
-      <c r="D149" t="s">
+      <c r="E149" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>355</v>
       </c>
@@ -3603,11 +3635,11 @@
       <c r="C150">
         <v>336</v>
       </c>
-      <c r="D150" t="s">
+      <c r="E150" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>355</v>
       </c>
@@ -3617,11 +3649,11 @@
       <c r="C151">
         <v>536</v>
       </c>
-      <c r="D151" t="s">
+      <c r="E151" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>355</v>
       </c>
@@ -3631,11 +3663,12 @@
       <c r="C152">
         <v>542</v>
       </c>
-      <c r="D152" s="5" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D152" s="5"/>
+      <c r="E152" s="5" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>355</v>
       </c>
@@ -3645,11 +3678,11 @@
       <c r="C153">
         <v>581</v>
       </c>
-      <c r="D153" t="s">
+      <c r="E153" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>355</v>
       </c>
@@ -3660,7 +3693,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>355</v>
       </c>
@@ -3670,11 +3703,11 @@
       <c r="C155">
         <v>305</v>
       </c>
-      <c r="D155" t="s">
+      <c r="E155" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>355</v>
       </c>
@@ -3684,11 +3717,11 @@
       <c r="C156">
         <v>550</v>
       </c>
-      <c r="D156" t="s">
+      <c r="E156" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>355</v>
       </c>
@@ -3698,11 +3731,11 @@
       <c r="C157">
         <v>540</v>
       </c>
-      <c r="D157" t="s">
+      <c r="E157" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>355</v>
       </c>
@@ -3713,7 +3746,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>355</v>
       </c>
@@ -3723,11 +3756,11 @@
       <c r="C159">
         <v>120</v>
       </c>
-      <c r="D159" t="s">
+      <c r="E159" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>355</v>
       </c>
@@ -3738,7 +3771,7 @@
         <v>139.5</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>355</v>
       </c>
@@ -3748,11 +3781,11 @@
       <c r="C161">
         <v>230</v>
       </c>
-      <c r="D161" t="s">
+      <c r="E161" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>355</v>
       </c>
@@ -3763,7 +3796,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>355</v>
       </c>
@@ -3773,11 +3806,11 @@
       <c r="C163">
         <v>118</v>
       </c>
-      <c r="D163" t="s">
+      <c r="E163" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>355</v>
       </c>
@@ -3788,7 +3821,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>355</v>
       </c>
@@ -3799,7 +3832,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>355</v>
       </c>
@@ -3810,7 +3843,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>355</v>
       </c>
@@ -3820,11 +3853,11 @@
       <c r="C167">
         <v>150</v>
       </c>
-      <c r="D167" t="s">
+      <c r="E167" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>355</v>
       </c>
@@ -3835,7 +3868,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>355</v>
       </c>
@@ -3845,11 +3878,11 @@
       <c r="C169">
         <v>170</v>
       </c>
-      <c r="D169" t="s">
+      <c r="E169" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>355</v>
       </c>
@@ -3859,11 +3892,11 @@
       <c r="C170">
         <v>175</v>
       </c>
-      <c r="D170" t="s">
+      <c r="E170" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>355</v>
       </c>
@@ -3874,7 +3907,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>296</v>
       </c>
@@ -3884,11 +3917,11 @@
       <c r="C172">
         <v>680</v>
       </c>
-      <c r="D172" t="s">
+      <c r="E172" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>370</v>
       </c>
@@ -3899,7 +3932,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>370</v>
       </c>
@@ -3909,11 +3942,11 @@
       <c r="C174">
         <v>335</v>
       </c>
-      <c r="D174" t="s">
+      <c r="E174" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>372</v>
       </c>
@@ -3923,11 +3956,11 @@
       <c r="C175">
         <v>156</v>
       </c>
-      <c r="D175" t="s">
+      <c r="E175" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>374</v>
       </c>
@@ -3938,7 +3971,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>374</v>
       </c>
@@ -3949,7 +3982,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>375</v>
       </c>
@@ -3959,11 +3992,11 @@
       <c r="C178">
         <v>1219</v>
       </c>
-      <c r="D178" t="s">
+      <c r="E178" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>377</v>
       </c>
@@ -3974,7 +4007,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>377</v>
       </c>
@@ -3985,7 +4018,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>378</v>
       </c>
@@ -3995,11 +4028,11 @@
       <c r="C181">
         <v>60</v>
       </c>
-      <c r="D181" t="s">
+      <c r="E181" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>380</v>
       </c>
@@ -4009,11 +4042,11 @@
       <c r="C182">
         <v>168</v>
       </c>
-      <c r="D182" t="s">
+      <c r="E182" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>382</v>
       </c>
@@ -4023,11 +4056,11 @@
       <c r="C183">
         <v>1000</v>
       </c>
-      <c r="D183" t="s">
+      <c r="E183" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>380</v>
       </c>
@@ -4037,11 +4070,11 @@
       <c r="C184">
         <v>1000</v>
       </c>
-      <c r="D184" t="s">
+      <c r="E184" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>384</v>
       </c>
@@ -4052,7 +4085,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>385</v>
       </c>
@@ -4063,7 +4096,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>386</v>
       </c>
@@ -4074,7 +4107,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>386</v>
       </c>
@@ -4084,11 +4117,11 @@
       <c r="C188">
         <v>68</v>
       </c>
-      <c r="D188" t="s">
+      <c r="E188" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>386</v>
       </c>
@@ -4098,11 +4131,11 @@
       <c r="C189">
         <v>50</v>
       </c>
-      <c r="D189" t="s">
+      <c r="E189" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>386</v>
       </c>
@@ -4112,11 +4145,11 @@
       <c r="C190">
         <v>81</v>
       </c>
-      <c r="D190" t="s">
+      <c r="E190" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>386</v>
       </c>
@@ -4127,7 +4160,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>386</v>
       </c>
@@ -4138,7 +4171,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>386</v>
       </c>
@@ -4149,7 +4182,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>386</v>
       </c>
@@ -4160,7 +4193,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>386</v>
       </c>
@@ -4170,11 +4203,11 @@
       <c r="C195">
         <v>180</v>
       </c>
-      <c r="D195" t="s">
+      <c r="E195" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>391</v>
       </c>
@@ -4184,11 +4217,11 @@
       <c r="C196">
         <v>48</v>
       </c>
-      <c r="D196" t="s">
+      <c r="E196" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>393</v>
       </c>
@@ -4199,7 +4232,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>393</v>
       </c>
@@ -4210,7 +4243,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>394</v>
       </c>
@@ -4221,7 +4254,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>395</v>
       </c>
@@ -4229,226 +4262,190 @@
         <v>1.8</v>
       </c>
       <c r="C200">
-        <v>202</v>
-      </c>
-      <c r="D200" t="s">
+        <v>335</v>
+      </c>
+      <c r="D200">
+        <v>0.19170000000000001</v>
+      </c>
+      <c r="E200" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>395</v>
-      </c>
-      <c r="B201">
-        <v>1.8</v>
-      </c>
-      <c r="C201">
-        <v>225</v>
-      </c>
-      <c r="D201" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+        <v>397</v>
+      </c>
+      <c r="B201" s="6">
+        <v>5.9</v>
+      </c>
+      <c r="E201" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>395</v>
-      </c>
-      <c r="B202">
-        <v>1.8</v>
-      </c>
-      <c r="C202">
-        <v>335</v>
-      </c>
-      <c r="D202" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+        <v>397</v>
+      </c>
+      <c r="B202" s="6">
+        <v>6</v>
+      </c>
+      <c r="E202" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>370</v>
-      </c>
-      <c r="B203">
-        <v>1.8</v>
-      </c>
-      <c r="C203">
-        <v>335</v>
-      </c>
-      <c r="D203" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B203" s="6">
+        <v>6.9</v>
+      </c>
+      <c r="E203" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B204" s="6">
-        <v>5.9</v>
-      </c>
-      <c r="D204" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="E204" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B205" s="6">
+        <v>7.35</v>
+      </c>
+      <c r="E205" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>397</v>
+      </c>
+      <c r="B206" s="6">
+        <v>7.45</v>
+      </c>
+      <c r="E206" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>397</v>
+      </c>
+      <c r="B207" s="6">
+        <v>8</v>
+      </c>
+      <c r="E207" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>405</v>
+      </c>
+      <c r="B208" s="6">
         <v>6</v>
       </c>
-      <c r="D205" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A206" t="s">
-        <v>398</v>
-      </c>
-      <c r="B206" s="6">
-        <v>6.9</v>
-      </c>
-      <c r="D206" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A207" t="s">
-        <v>398</v>
-      </c>
-      <c r="B207" s="6">
-        <v>7</v>
-      </c>
-      <c r="D207" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A208" t="s">
-        <v>398</v>
-      </c>
-      <c r="B208" s="6">
+      <c r="E208" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>407</v>
+      </c>
+      <c r="B209" s="6">
         <v>7.35</v>
       </c>
-      <c r="D208" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A209" t="s">
-        <v>398</v>
-      </c>
-      <c r="B209" s="6">
-        <v>7.45</v>
-      </c>
-      <c r="D209" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E209" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="B210" s="6">
-        <v>8</v>
-      </c>
-      <c r="D210" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B211" s="6">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>411</v>
+      </c>
+      <c r="B212" s="6">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>412</v>
+      </c>
+      <c r="B213" s="6">
         <v>6</v>
       </c>
-      <c r="D211" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A212" t="s">
-        <v>408</v>
-      </c>
-      <c r="B212" s="6">
-        <v>7.35</v>
-      </c>
-      <c r="D212" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A213" t="s">
-        <v>410</v>
-      </c>
-      <c r="B213" s="6">
-        <v>7.9</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A214" t="s">
-        <v>411</v>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A214" s="5" t="s">
+        <v>414</v>
       </c>
       <c r="B214" s="6">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A215" t="s">
-        <v>412</v>
+        <v>5</v>
+      </c>
+      <c r="C214">
+        <v>394</v>
+      </c>
+      <c r="D214" s="5"/>
+      <c r="E214" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="F214" s="5"/>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A215" s="5" t="s">
+        <v>416</v>
       </c>
       <c r="B215" s="6">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A216" t="s">
-        <v>413</v>
+        <v>4.5</v>
+      </c>
+      <c r="C215">
+        <v>174</v>
+      </c>
+      <c r="D215" s="5"/>
+      <c r="E215" s="5" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A216" s="5" t="s">
+        <v>416</v>
       </c>
       <c r="B216" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A217" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="B217" s="6">
-        <v>5</v>
-      </c>
-      <c r="C217">
-        <v>394</v>
-      </c>
-      <c r="D217" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="E217" s="5"/>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A218" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="B218" s="6">
         <v>4.5</v>
       </c>
-      <c r="C218">
-        <v>174</v>
-      </c>
-      <c r="D218" s="5" t="s">
+      <c r="C216">
+        <v>226</v>
+      </c>
+      <c r="D216" s="5"/>
+      <c r="E216" s="5" t="s">
         <v>418</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A219" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="B219" s="6">
-        <v>4.5</v>
-      </c>
-      <c r="C219">
-        <v>226</v>
-      </c>
-      <c r="D219" s="5" t="s">
-        <v>419</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4716784bbc33fc8c/바탕 화면/앱 관련/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{8D6AD43F-F395-4691-843B-740155F5A6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCF19CE5-8C0A-49D1-A50B-BB5B2369E01B}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="8_{8D6AD43F-F395-4691-843B-740155F5A6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BBF26C9-1BA4-48AA-8BE2-B589A60D6637}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{524E4321-34C6-4851-BBC3-552957EB36E1}"/>
+    <workbookView xWindow="9225" yWindow="660" windowWidth="28800" windowHeight="11295" xr2:uid="{524E4321-34C6-4851-BBC3-552957EB36E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="425">
   <si>
     <t>SPFH590 2.0*148</t>
   </si>
@@ -842,18 +842,12 @@
     <t>(AJ LOWER)</t>
   </si>
   <si>
-    <t>반납</t>
-  </si>
-  <si>
     <t>(D031 LWR)</t>
   </si>
   <si>
     <t>(D051 LWR)</t>
   </si>
   <si>
-    <t>(사용금지)</t>
-  </si>
-  <si>
     <t>(C100 FRAME)</t>
   </si>
   <si>
@@ -884,15 +878,6 @@
     <t>C1100-1/2H</t>
   </si>
   <si>
-    <t>(BUSBAR INV MINUS)</t>
-  </si>
-  <si>
-    <t>(BUSBAR INV PLUS 외 공용)</t>
-  </si>
-  <si>
-    <t>(BATT PLUS 1 BUSBAR)</t>
-  </si>
-  <si>
     <t>SGHC</t>
   </si>
   <si>
@@ -936,9 +921,6 @@
   </si>
   <si>
     <t>(PRB COVER REAR)</t>
-  </si>
-  <si>
-    <t>(PRE CORE PLATE) 대운테</t>
   </si>
   <si>
     <t>(PRB DRIVEN PLATE)</t>
@@ -1290,6 +1272,50 @@
   </si>
   <si>
     <t>제품 단중</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>고객사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AT&amp;S</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>구산</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(PRE CORE PLATE)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>세바</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOTOR CASE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(BUSBAR 48번)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(BUSBAR 49번)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(BUSBAR 50번)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(BUSBAR 51번)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(BUSBAR 52번)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1297,8 +1323,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.0"/>
+    <numFmt numFmtId="180" formatCode="0.000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -1399,7 +1426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1415,6 +1442,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1430,6 +1458,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1719,16 +1751,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6849FD11-1D35-422D-825C-843B8DFC35E0}">
-  <dimension ref="A1:F216"/>
+  <dimension ref="A1:F215"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="7.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>256</v>
       </c>
@@ -1739,24 +1773,36 @@
         <v>258</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="E1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>281</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>259</v>
       </c>
       <c r="B2">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="C2">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+      <c r="D2">
+        <v>0.17219999999999999</v>
+      </c>
+      <c r="E2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>259</v>
       </c>
@@ -1764,33 +1810,30 @@
         <v>1.3</v>
       </c>
       <c r="C3">
-        <v>212</v>
+        <v>272</v>
       </c>
       <c r="D3">
-        <v>0.17219999999999999</v>
+        <v>0.19570000000000001</v>
       </c>
       <c r="E3" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>259</v>
       </c>
       <c r="B4">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="C4">
-        <v>272</v>
-      </c>
-      <c r="D4">
-        <v>0.19570000000000001</v>
-      </c>
-      <c r="E4" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>259</v>
       </c>
@@ -1798,10 +1841,10 @@
         <v>1.4</v>
       </c>
       <c r="C5">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>259</v>
       </c>
@@ -1809,27 +1852,30 @@
         <v>1.4</v>
       </c>
       <c r="C6">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>281</v>
+      </c>
+      <c r="D6">
+        <v>0.22850000000000001</v>
+      </c>
+      <c r="E6" t="s">
+        <v>262</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>259</v>
       </c>
       <c r="B7">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="C7">
-        <v>281</v>
-      </c>
-      <c r="D7">
-        <v>0.22850000000000001</v>
-      </c>
-      <c r="E7" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>259</v>
       </c>
@@ -1837,66 +1883,69 @@
         <v>1.5</v>
       </c>
       <c r="C8">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>238</v>
+      </c>
+      <c r="D8">
+        <v>0.1361</v>
+      </c>
+      <c r="E8" t="s">
+        <v>263</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>259</v>
       </c>
       <c r="B9">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="C9">
-        <v>238</v>
-      </c>
-      <c r="D9">
-        <v>0.1361</v>
+        <v>160</v>
       </c>
       <c r="E9" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>259</v>
       </c>
       <c r="B10">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="E10" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="C11">
-        <v>190</v>
-      </c>
-      <c r="E11" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+        <v>119.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>266</v>
       </c>
       <c r="B12">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="C12">
-        <v>119.8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>266</v>
       </c>
@@ -1904,10 +1953,10 @@
         <v>1.8</v>
       </c>
       <c r="C13">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>266</v>
       </c>
@@ -1915,10 +1964,10 @@
         <v>1.8</v>
       </c>
       <c r="C14">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>266</v>
       </c>
@@ -1926,10 +1975,10 @@
         <v>1.8</v>
       </c>
       <c r="C15">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>266</v>
       </c>
@@ -1937,10 +1986,10 @@
         <v>1.8</v>
       </c>
       <c r="C16">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+        <v>144.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>266</v>
       </c>
@@ -1948,10 +1997,19 @@
         <v>1.8</v>
       </c>
       <c r="C17">
-        <v>144.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+        <v>238</v>
+      </c>
+      <c r="D17">
+        <v>0.21099999999999999</v>
+      </c>
+      <c r="E17" t="s">
+        <v>267</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>266</v>
       </c>
@@ -1959,16 +2017,10 @@
         <v>1.8</v>
       </c>
       <c r="C18">
-        <v>238</v>
-      </c>
-      <c r="D18">
-        <v>0.21099999999999999</v>
-      </c>
-      <c r="E18" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>266</v>
       </c>
@@ -1976,10 +2028,10 @@
         <v>1.8</v>
       </c>
       <c r="C19">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>266</v>
       </c>
@@ -1987,10 +2039,19 @@
         <v>1.8</v>
       </c>
       <c r="C20">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+      <c r="D20">
+        <v>0.2359</v>
+      </c>
+      <c r="E20" t="s">
+        <v>268</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>266</v>
       </c>
@@ -1998,16 +2059,19 @@
         <v>1.8</v>
       </c>
       <c r="C21">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="D21">
-        <v>0.2359</v>
+        <v>0.24510000000000001</v>
       </c>
       <c r="E21" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+        <v>269</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>266</v>
       </c>
@@ -2015,16 +2079,10 @@
         <v>1.8</v>
       </c>
       <c r="C22">
-        <v>256</v>
-      </c>
-      <c r="D22">
-        <v>0.24510000000000001</v>
-      </c>
-      <c r="E22" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>266</v>
       </c>
@@ -2032,24 +2090,30 @@
         <v>1.8</v>
       </c>
       <c r="C23">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+      <c r="D23">
+        <v>0.27279999999999999</v>
+      </c>
+      <c r="E23" t="s">
+        <v>270</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>266</v>
       </c>
       <c r="B24">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>270</v>
-      </c>
-      <c r="E24" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>266</v>
       </c>
@@ -2057,10 +2121,10 @@
         <v>2</v>
       </c>
       <c r="C25">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>266</v>
       </c>
@@ -2068,24 +2132,39 @@
         <v>2</v>
       </c>
       <c r="C26">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+      <c r="D26">
+        <v>0.17219999999999999</v>
+      </c>
+      <c r="E26" t="s">
+        <v>271</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>266</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="C27">
-        <v>204</v>
+        <v>179</v>
+      </c>
+      <c r="D27">
+        <v>0.1394</v>
       </c>
       <c r="E27" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+        <v>272</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>266</v>
       </c>
@@ -2093,13 +2172,19 @@
         <v>2.1</v>
       </c>
       <c r="C28">
-        <v>77</v>
+        <v>192</v>
+      </c>
+      <c r="D28">
+        <v>0.16059999999999999</v>
       </c>
       <c r="E28" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+        <v>273</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>266</v>
       </c>
@@ -2107,202 +2192,220 @@
         <v>2.1</v>
       </c>
       <c r="C29">
-        <v>179</v>
-      </c>
-      <c r="D29">
-        <v>0.1394</v>
-      </c>
-      <c r="E29" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>266</v>
       </c>
       <c r="B30">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="C30">
-        <v>192</v>
-      </c>
-      <c r="D30">
-        <v>0.16059999999999999</v>
+        <v>170</v>
       </c>
       <c r="E30" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>266</v>
       </c>
       <c r="B31">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="C31">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>266</v>
       </c>
       <c r="B32">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="C32">
-        <v>204</v>
+        <v>335</v>
       </c>
       <c r="E32" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>266</v>
       </c>
       <c r="B33">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
       <c r="C33">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="E33" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>266</v>
       </c>
       <c r="B34">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="C34">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+        <v>589</v>
+      </c>
+      <c r="E34" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>266</v>
       </c>
       <c r="B35">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="C35">
-        <v>335</v>
+        <v>108</v>
       </c>
       <c r="E35" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>266</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C36">
-        <v>108</v>
+        <v>164</v>
       </c>
       <c r="E36" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>266</v>
       </c>
       <c r="B37">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="C37">
-        <v>589</v>
-      </c>
-      <c r="E37" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="B38">
         <v>4</v>
       </c>
       <c r="C38">
-        <v>108</v>
-      </c>
-      <c r="E38" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="C39">
-        <v>164</v>
-      </c>
-      <c r="E39" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="B40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C40">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+      <c r="D40" s="7">
+        <v>0.25414632000000004</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C41">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+      <c r="D41" s="7">
+        <v>0.13066704000000001</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B42">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+      <c r="D42" s="7">
+        <v>0.24888960000000002</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B43">
         <v>3</v>
       </c>
       <c r="C43">
-        <v>103</v>
-      </c>
-      <c r="E43" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+      <c r="D43" s="7">
+        <v>0.22979376000000001</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B44">
         <v>3</v>
@@ -2310,2142 +2413,2158 @@
       <c r="C44">
         <v>116</v>
       </c>
-      <c r="E44" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D44" s="7">
+        <v>0.11200032000000001</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="C45">
-        <v>119</v>
-      </c>
-      <c r="E45" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>284</v>
       </c>
       <c r="B46">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="C46">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+        <v>70.400000000000006</v>
+      </c>
+      <c r="E46" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B47">
         <v>2.6</v>
       </c>
       <c r="C47">
-        <v>70.400000000000006</v>
-      </c>
-      <c r="E47" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B48">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="C48">
-        <v>114</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="C49">
-        <v>40</v>
+        <v>234</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B50">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="C50">
-        <v>234</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B51">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="C51">
-        <v>110</v>
+        <v>170</v>
+      </c>
+      <c r="E51" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B52">
         <v>5</v>
       </c>
       <c r="C52">
-        <v>170</v>
-      </c>
-      <c r="E52" t="s">
-        <v>295</v>
+        <v>172</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B53">
         <v>5</v>
       </c>
       <c r="C53">
-        <v>172</v>
+        <v>306</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B54">
         <v>5</v>
       </c>
       <c r="C54">
-        <v>306</v>
+        <v>402</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B55">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="C55">
-        <v>402</v>
+        <v>413</v>
+      </c>
+      <c r="E55" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B56">
         <v>1.6</v>
       </c>
       <c r="C56">
-        <v>413</v>
-      </c>
-      <c r="E56" t="s">
-        <v>297</v>
+        <v>447</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B57">
         <v>1.6</v>
       </c>
       <c r="C57">
-        <v>447</v>
+        <v>473</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B58">
         <v>1.6</v>
       </c>
       <c r="C58">
-        <v>473</v>
+        <v>520</v>
+      </c>
+      <c r="E58" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B59">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>520</v>
-      </c>
-      <c r="E59" t="s">
-        <v>299</v>
+        <v>95</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B60">
         <v>2</v>
       </c>
       <c r="C60">
-        <v>95</v>
+        <v>334</v>
+      </c>
+      <c r="E60" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B61">
         <v>2</v>
       </c>
       <c r="C61">
-        <v>334</v>
+        <v>500</v>
       </c>
       <c r="E61" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E62" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
       <c r="C63">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="E63" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64">
-        <v>512</v>
-      </c>
-      <c r="E64" t="s">
-        <v>303</v>
+        <v>522</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
       <c r="C65">
-        <v>522</v>
+        <v>530</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B66">
         <v>2</v>
       </c>
       <c r="C66">
-        <v>530</v>
+        <v>537</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="C67">
-        <v>537</v>
+        <v>514</v>
       </c>
       <c r="E67" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B68">
         <v>2.2999999999999998</v>
       </c>
       <c r="C68">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="E68" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B69">
         <v>2.2999999999999998</v>
       </c>
       <c r="C69">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="E69" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B70">
-        <v>2.2999999999999998</v>
+        <v>2.6</v>
       </c>
       <c r="C70">
-        <v>529</v>
+        <v>160</v>
       </c>
       <c r="E70" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B71">
         <v>2.6</v>
       </c>
       <c r="C71">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="E71" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B72">
         <v>2.6</v>
       </c>
       <c r="C72">
-        <v>210</v>
-      </c>
-      <c r="E72" t="s">
-        <v>309</v>
+        <v>355</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B73">
         <v>2.6</v>
       </c>
       <c r="C73">
-        <v>355</v>
+        <v>495</v>
+      </c>
+      <c r="E73" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B74">
         <v>2.6</v>
       </c>
       <c r="C74">
-        <v>495</v>
-      </c>
-      <c r="E74" t="s">
-        <v>310</v>
+        <v>544</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B75">
         <v>2.6</v>
       </c>
       <c r="C75">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B76">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="C76">
-        <v>545</v>
+        <v>392</v>
+      </c>
+      <c r="E76" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B77">
         <v>2.8</v>
       </c>
       <c r="C77">
-        <v>392</v>
+        <v>641</v>
       </c>
       <c r="E77" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B78">
         <v>2.8</v>
       </c>
       <c r="C78">
-        <v>641</v>
-      </c>
-      <c r="E78" t="s">
-        <v>312</v>
+        <v>656</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B79">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="C79">
-        <v>656</v>
+        <v>195</v>
+      </c>
+      <c r="E79" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B80">
         <v>3</v>
       </c>
       <c r="C80">
-        <v>195</v>
+        <v>525</v>
       </c>
       <c r="E80" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B81">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="C81">
-        <v>525</v>
+        <v>106</v>
       </c>
       <c r="E81" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B82">
         <v>3.2</v>
       </c>
       <c r="C82">
-        <v>106</v>
+        <v>514</v>
       </c>
       <c r="E82" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B83">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="C83">
-        <v>514</v>
+        <v>153</v>
       </c>
       <c r="E83" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B84">
         <v>4</v>
       </c>
       <c r="C84">
-        <v>153</v>
-      </c>
-      <c r="E84" t="s">
-        <v>317</v>
+        <v>160</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B85">
         <v>4</v>
       </c>
       <c r="C85">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B86">
         <v>4</v>
       </c>
       <c r="C86">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B87">
         <v>4</v>
       </c>
       <c r="C87">
-        <v>168</v>
+        <v>382</v>
+      </c>
+      <c r="E87" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B88">
         <v>4</v>
       </c>
       <c r="C88">
-        <v>382</v>
+        <v>585</v>
       </c>
       <c r="E88" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B89">
         <v>4</v>
       </c>
       <c r="C89">
-        <v>585</v>
-      </c>
-      <c r="E89" t="s">
-        <v>319</v>
+        <v>627</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B90">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C90">
-        <v>627</v>
+        <v>590</v>
+      </c>
+      <c r="E90" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B91">
         <v>5</v>
       </c>
       <c r="C91">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="E91" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B92">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="C92">
-        <v>602</v>
+        <v>654</v>
       </c>
       <c r="E92" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="B93">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="C93">
-        <v>654</v>
-      </c>
-      <c r="E93" t="s">
-        <v>322</v>
+        <v>237</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B94">
         <v>2</v>
       </c>
       <c r="C94">
-        <v>237</v>
+        <v>314</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="C95">
-        <v>314</v>
+        <v>70</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B96">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C96">
-        <v>70</v>
+        <v>102</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B97">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="C97">
-        <v>102</v>
+        <v>331</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B98">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="C98">
-        <v>331</v>
+        <v>234</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B99">
-        <v>2</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="C99">
-        <v>234</v>
+        <v>508</v>
+      </c>
+      <c r="E99" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B100">
         <v>2.2999999999999998</v>
       </c>
       <c r="C100">
-        <v>508</v>
+        <v>530</v>
       </c>
       <c r="E100" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B101">
-        <v>2.2999999999999998</v>
+        <v>2.6</v>
       </c>
       <c r="C101">
-        <v>530</v>
+        <v>508</v>
       </c>
       <c r="E101" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B102">
-        <v>2.6</v>
+        <v>0.75</v>
       </c>
       <c r="C102">
-        <v>508</v>
+        <v>96</v>
       </c>
       <c r="E102" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B103">
-        <v>0.75</v>
+        <v>4</v>
       </c>
       <c r="C103">
-        <v>96</v>
+        <v>186</v>
       </c>
       <c r="E103" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B104">
         <v>4</v>
       </c>
       <c r="C104">
-        <v>186</v>
+        <v>1230</v>
       </c>
       <c r="E104" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B105">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C105">
-        <v>1230</v>
-      </c>
-      <c r="E105" t="s">
-        <v>333</v>
+        <v>185</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B106">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="C106">
-        <v>185</v>
+        <v>41</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B107">
         <v>0.5</v>
       </c>
       <c r="C107">
-        <v>41</v>
+        <v>52</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B108">
         <v>0.5</v>
       </c>
       <c r="C108">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B109">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="C109">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B110">
         <v>0.6</v>
       </c>
       <c r="C110">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B111">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="C111">
-        <v>72</v>
+        <v>27</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>34</v>
+        <v>72</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="C114">
-        <v>72</v>
+        <v>65</v>
+      </c>
+      <c r="E114" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B115">
         <v>1.2</v>
       </c>
       <c r="C115">
-        <v>65</v>
+        <v>165</v>
       </c>
       <c r="E115" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B116">
         <v>1.2</v>
       </c>
       <c r="C116">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="E116" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B117">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="C117">
-        <v>184</v>
-      </c>
-      <c r="E117" t="s">
-        <v>337</v>
+        <v>60</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B118">
         <v>1.4</v>
       </c>
       <c r="C118">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B119">
         <v>1.4</v>
       </c>
       <c r="C119">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B120">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="C120">
-        <v>74</v>
+        <v>28</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B121">
         <v>1.5</v>
       </c>
       <c r="C121">
-        <v>28</v>
+        <v>69</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B122">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="C122">
-        <v>69</v>
+        <v>241</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B123">
         <v>1.6</v>
       </c>
       <c r="C123">
-        <v>241</v>
+        <v>336</v>
+      </c>
+      <c r="E123" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B124">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="C124">
-        <v>336</v>
-      </c>
-      <c r="E124" t="s">
-        <v>338</v>
+        <v>27</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B125">
         <v>2</v>
       </c>
       <c r="C125">
-        <v>27</v>
+        <v>50</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B126">
         <v>2</v>
       </c>
       <c r="C126">
-        <v>50</v>
+        <v>69</v>
+      </c>
+      <c r="E126" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B127">
         <v>2</v>
       </c>
       <c r="C127">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="E127" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B128">
-        <v>2</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="C128">
-        <v>117</v>
+        <v>1219</v>
       </c>
       <c r="E128" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B129">
-        <v>2.2999999999999998</v>
+        <v>2.6</v>
       </c>
       <c r="C129">
-        <v>1219</v>
-      </c>
-      <c r="E129" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B130">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="C130">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+      <c r="E130" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B131">
         <v>3</v>
       </c>
       <c r="C131">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E131" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B132">
-        <v>3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="C132">
-        <v>52</v>
-      </c>
-      <c r="E132" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="B133">
+        <v>2.6</v>
+      </c>
+      <c r="C133">
+        <v>267</v>
+      </c>
+      <c r="D133">
+        <v>0.38669999999999999</v>
+      </c>
+      <c r="E133" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="F133" s="5" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>339</v>
+      </c>
+      <c r="B134">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C133">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
-        <v>344</v>
-      </c>
-      <c r="B134">
-        <v>2.6</v>
-      </c>
       <c r="C134">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B135">
         <v>2.2999999999999998</v>
       </c>
       <c r="C135">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B136">
-        <v>2.2999999999999998</v>
+        <v>1.6</v>
       </c>
       <c r="C136">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B137">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="C137">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B138">
         <v>2</v>
       </c>
       <c r="C138">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+      <c r="E138" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B139">
         <v>2</v>
       </c>
       <c r="C139">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="E139" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B140">
         <v>2</v>
       </c>
       <c r="C140">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="E140" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B141">
         <v>2</v>
       </c>
       <c r="C141">
-        <v>131</v>
+        <v>180</v>
       </c>
       <c r="E141" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
+        <v>340</v>
+      </c>
+      <c r="B142">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C142">
+        <v>223.5</v>
+      </c>
+      <c r="E142" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>340</v>
+      </c>
+      <c r="B143">
+        <v>4</v>
+      </c>
+      <c r="C143">
+        <v>59</v>
+      </c>
+      <c r="E143" t="s">
         <v>346</v>
       </c>
-      <c r="B142">
-        <v>2</v>
-      </c>
-      <c r="C142">
-        <v>180</v>
-      </c>
-      <c r="E142" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
-        <v>346</v>
-      </c>
-      <c r="B143">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="C143">
-        <v>223.5</v>
-      </c>
-      <c r="E143" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B144">
         <v>4</v>
       </c>
       <c r="C144">
-        <v>59</v>
-      </c>
-      <c r="E144" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B145">
         <v>4</v>
       </c>
       <c r="C145">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+      <c r="E145" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B146">
         <v>4</v>
       </c>
       <c r="C146">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="E146" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B147">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="C147">
-        <v>202</v>
-      </c>
-      <c r="E147" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B148">
         <v>1.6</v>
       </c>
       <c r="C148">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+      <c r="E148" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B149">
         <v>1.6</v>
       </c>
       <c r="C149">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="E149" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B150">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="C150">
-        <v>336</v>
+        <v>536</v>
       </c>
       <c r="E150" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B151">
         <v>1.8</v>
       </c>
       <c r="C151">
-        <v>536</v>
-      </c>
-      <c r="E151" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+        <v>542</v>
+      </c>
+      <c r="D151" s="5"/>
+      <c r="E151" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="F151" s="5"/>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B152">
         <v>1.8</v>
       </c>
       <c r="C152">
-        <v>542</v>
-      </c>
-      <c r="D152" s="5"/>
-      <c r="E152" s="5" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+        <v>581</v>
+      </c>
+      <c r="E152" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B153">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="C153">
-        <v>581</v>
-      </c>
-      <c r="E153" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B154">
         <v>2</v>
       </c>
       <c r="C154">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+      <c r="E154" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B155">
         <v>2</v>
       </c>
       <c r="C155">
-        <v>305</v>
+        <v>550</v>
       </c>
       <c r="E155" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B156">
-        <v>2</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="C156">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="E156" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B157">
-        <v>2.2999999999999998</v>
+        <v>2.6</v>
       </c>
       <c r="C157">
-        <v>540</v>
-      </c>
-      <c r="E157" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B158">
         <v>2.6</v>
       </c>
       <c r="C158">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+      <c r="E158" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B159">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="C159">
-        <v>120</v>
-      </c>
-      <c r="E159" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+        <v>139.5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B160">
         <v>3</v>
       </c>
       <c r="C160">
-        <v>139.5</v>
+        <v>230</v>
+      </c>
+      <c r="E160" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B161">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="C161">
-        <v>230</v>
-      </c>
-      <c r="E161" t="s">
-        <v>364</v>
+        <v>64</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B162">
         <v>3.6</v>
       </c>
       <c r="C162">
-        <v>64</v>
+        <v>118</v>
+      </c>
+      <c r="E162" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B163">
         <v>3.6</v>
       </c>
       <c r="C163">
-        <v>118</v>
-      </c>
-      <c r="E163" t="s">
-        <v>365</v>
+        <v>120</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B164">
         <v>3.6</v>
       </c>
       <c r="C164">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B165">
         <v>3.6</v>
       </c>
       <c r="C165">
-        <v>124</v>
+        <v>143</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B166">
         <v>3.6</v>
       </c>
       <c r="C166">
-        <v>143</v>
+        <v>150</v>
+      </c>
+      <c r="E166" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B167">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="C167">
-        <v>150</v>
-      </c>
-      <c r="E167" t="s">
-        <v>366</v>
+        <v>86</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B168">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="C168">
-        <v>86</v>
+        <v>170</v>
+      </c>
+      <c r="E168" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B169">
         <v>4.5</v>
       </c>
       <c r="C169">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E169" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B170">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C170">
-        <v>175</v>
-      </c>
-      <c r="E170" t="s">
-        <v>368</v>
+        <v>170</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>355</v>
+        <v>291</v>
       </c>
       <c r="B171">
         <v>5</v>
       </c>
       <c r="C171">
-        <v>170</v>
+        <v>680</v>
+      </c>
+      <c r="E171" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>296</v>
+        <v>364</v>
       </c>
       <c r="B172">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="C172">
-        <v>680</v>
-      </c>
-      <c r="E172" t="s">
-        <v>369</v>
+        <v>74</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="B173">
         <v>1.8</v>
       </c>
       <c r="C173">
-        <v>74</v>
+        <v>335</v>
+      </c>
+      <c r="E173" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B174">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="C174">
-        <v>335</v>
+        <v>156</v>
       </c>
       <c r="E174" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B175">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="C175">
-        <v>156</v>
-      </c>
-      <c r="E175" t="s">
-        <v>373</v>
+        <v>315</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="B176">
         <v>2</v>
       </c>
       <c r="C176">
-        <v>315</v>
+        <v>480</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B177">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C177">
-        <v>480</v>
+        <v>1219</v>
+      </c>
+      <c r="E177" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B178">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="C178">
-        <v>1219</v>
-      </c>
-      <c r="E178" t="s">
-        <v>376</v>
+        <v>350</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B179">
         <v>1</v>
       </c>
       <c r="C179">
-        <v>350</v>
+        <v>378</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B180">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="C180">
-        <v>378</v>
+        <v>60</v>
+      </c>
+      <c r="E180" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B181">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="C181">
-        <v>60</v>
+        <v>168</v>
       </c>
       <c r="E181" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B182">
         <v>3</v>
       </c>
       <c r="C182">
-        <v>168</v>
+        <v>1000</v>
       </c>
       <c r="E182" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B183">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C183">
         <v>1000</v>
       </c>
       <c r="E183" t="s">
-        <v>383</v>
+        <v>327</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B184">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="C184">
-        <v>1000</v>
-      </c>
-      <c r="E184" t="s">
-        <v>333</v>
+        <v>107</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B185">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="C185">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B186">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="C186">
-        <v>92</v>
+        <v>59</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B187">
         <v>1.5</v>
       </c>
       <c r="C187">
-        <v>59</v>
+        <v>68</v>
+      </c>
+      <c r="E187" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B188">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="C188">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="E188" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B189">
         <v>2</v>
       </c>
       <c r="C189">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="E189" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B190">
         <v>2</v>
       </c>
       <c r="C190">
-        <v>81</v>
-      </c>
-      <c r="E190" t="s">
-        <v>389</v>
+        <v>84</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B191">
         <v>2</v>
       </c>
       <c r="C191">
-        <v>84</v>
+        <v>120</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B192">
         <v>2</v>
       </c>
       <c r="C192">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B193">
         <v>2</v>
       </c>
       <c r="C193">
-        <v>126</v>
+        <v>154</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B194">
         <v>2</v>
       </c>
       <c r="C194">
-        <v>154</v>
+        <v>180</v>
+      </c>
+      <c r="E194" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
+        <v>385</v>
+      </c>
+      <c r="B195">
+        <v>0.8</v>
+      </c>
+      <c r="C195">
+        <v>48</v>
+      </c>
+      <c r="E195" t="s">
         <v>386</v>
-      </c>
-      <c r="B195">
-        <v>2</v>
-      </c>
-      <c r="C195">
-        <v>180</v>
-      </c>
-      <c r="E195" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B196">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C196">
-        <v>48</v>
-      </c>
-      <c r="E196" t="s">
-        <v>392</v>
+        <v>92</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B197">
         <v>1</v>
       </c>
       <c r="C197">
-        <v>92</v>
+        <v>156</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B198">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="C198">
-        <v>156</v>
+        <v>330</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B199">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="C199">
-        <v>330</v>
+        <v>335</v>
+      </c>
+      <c r="D199">
+        <v>0.19170000000000001</v>
+      </c>
+      <c r="E199" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>395</v>
-      </c>
-      <c r="B200">
-        <v>1.8</v>
-      </c>
-      <c r="C200">
-        <v>335</v>
-      </c>
-      <c r="D200">
-        <v>0.19170000000000001</v>
+        <v>391</v>
+      </c>
+      <c r="B200" s="6">
+        <v>5.9</v>
       </c>
       <c r="E200" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="B201" s="6">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="E201" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="B202" s="6">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="E202" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="B203" s="6">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="E203" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="B204" s="6">
-        <v>7</v>
+        <v>7.35</v>
       </c>
       <c r="E204" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
+        <v>391</v>
+      </c>
+      <c r="B205" s="6">
+        <v>7.45</v>
+      </c>
+      <c r="E205" t="s">
         <v>397</v>
-      </c>
-      <c r="B205" s="6">
-        <v>7.35</v>
-      </c>
-      <c r="E205" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="B206" s="6">
-        <v>7.45</v>
+        <v>8</v>
       </c>
       <c r="E206" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B207" s="6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E207" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B208" s="6">
-        <v>6</v>
+        <v>7.35</v>
       </c>
       <c r="E208" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B209" s="6">
-        <v>7.35</v>
-      </c>
-      <c r="E209" t="s">
-        <v>408</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B210" s="6">
-        <v>7.9</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B211" s="6">
-        <v>7.25</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B212" s="6">
-        <v>6.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A213" t="s">
-        <v>412</v>
+      <c r="A213" s="5" t="s">
+        <v>408</v>
       </c>
       <c r="B213" s="6">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="C213">
+        <v>394</v>
+      </c>
+      <c r="D213" s="5">
+        <v>4.2050000000000001</v>
+      </c>
+      <c r="E213" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="F213" s="5" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="5" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B214" s="6">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C214">
-        <v>394</v>
-      </c>
-      <c r="D214" s="5"/>
+        <v>174</v>
+      </c>
+      <c r="D214" s="5">
+        <v>0.505</v>
+      </c>
       <c r="E214" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="F214" s="5"/>
+        <v>411</v>
+      </c>
+      <c r="F214" s="5" t="s">
+        <v>416</v>
+      </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="5" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="B215" s="6">
         <v>4.5</v>
       </c>
       <c r="C215">
-        <v>174</v>
-      </c>
-      <c r="D215" s="5"/>
+        <v>226</v>
+      </c>
+      <c r="D215" s="5">
+        <v>1.93</v>
+      </c>
       <c r="E215" s="5" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A216" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="F215" s="5" t="s">
         <v>416</v>
-      </c>
-      <c r="B216" s="6">
-        <v>4.5</v>
-      </c>
-      <c r="C216">
-        <v>226</v>
-      </c>
-      <c r="D216" s="5"/>
-      <c r="E216" s="5" t="s">
-        <v>418</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4716784bbc33fc8c/바탕 화면/앱 관련/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="8_{8D6AD43F-F395-4691-843B-740155F5A6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BBF26C9-1BA4-48AA-8BE2-B589A60D6637}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="8_{8D6AD43F-F395-4691-843B-740155F5A6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07F3C4D7-1463-48B2-BF88-335B9A77CB12}"/>
   <bookViews>
-    <workbookView xWindow="9225" yWindow="660" windowWidth="28800" windowHeight="11295" xr2:uid="{524E4321-34C6-4851-BBC3-552957EB36E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{524E4321-34C6-4851-BBC3-552957EB36E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="428">
   <si>
     <t>SPFH590 2.0*148</t>
   </si>
@@ -806,48 +806,9 @@
     <t>SPFC590</t>
   </si>
   <si>
-    <t>(E0621 LOWER)</t>
-  </si>
-  <si>
-    <t>(E0621 UPPER)</t>
-  </si>
-  <si>
-    <t>(PH5 UPR)</t>
-  </si>
-  <si>
-    <t>(PH5 LWR)</t>
-  </si>
-  <si>
-    <t>(VW360 BACK PLT)</t>
-  </si>
-  <si>
-    <t>(VW360 FRAME)</t>
-  </si>
-  <si>
     <t>SPFH590</t>
   </si>
   <si>
-    <t>(AS / AT / AU)</t>
-  </si>
-  <si>
-    <t>(AA / AD / AG)</t>
-  </si>
-  <si>
-    <t>(AH / AM)</t>
-  </si>
-  <si>
-    <t>(AJ / AN)</t>
-  </si>
-  <si>
-    <t>(AJ LOWER)</t>
-  </si>
-  <si>
-    <t>(D031 LWR)</t>
-  </si>
-  <si>
-    <t>(D051 LWR)</t>
-  </si>
-  <si>
     <t>(C100 FRAME)</t>
   </si>
   <si>
@@ -869,9 +830,6 @@
     <t>SPFH590P</t>
   </si>
   <si>
-    <t>기타 정보 및 사양</t>
-  </si>
-  <si>
     <t>C2680R 1/2H</t>
   </si>
   <si>
@@ -1106,9 +1064,6 @@
     <t>(LIFT BASE BACK PLT)</t>
   </si>
   <si>
-    <t>(LM, YB T/G STK)</t>
-  </si>
-  <si>
     <t>(FLANG 小)</t>
   </si>
   <si>
@@ -1196,9 +1151,6 @@
     <t>SGMCD3</t>
   </si>
   <si>
-    <t>(NEM / NGM 포스맥)</t>
-  </si>
-  <si>
     <t>SCM435</t>
   </si>
   <si>
@@ -1209,9 +1161,6 @@
   </si>
   <si>
     <t>(규격 Ø6.9)</t>
-  </si>
-  <si>
-    <t>(LM SHAFT)</t>
   </si>
   <si>
     <t>(GEN2 SIDE, GL-1 LOOP)</t>
@@ -1255,10 +1204,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>PULLEY 0697</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>SPHD</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1299,23 +1244,107 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>(BUSBAR 48번)</t>
+    <t>BUS 48</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>(BUSBAR 49번)</t>
+    <t>BUS 49</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>(BUSBAR 50번)</t>
+    <t>BUS 50</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>(BUSBAR 51번)</t>
+    <t>BUS 51</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>(BUSBAR 52번)</t>
+    <t>BUS 52</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로젝트명</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PH5 U</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>E0621 L</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>E0621 U</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PH5 L</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>VW360 B</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>VW360 F</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AS U</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AA U</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AH U</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AJ U</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AJ L</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>031 L</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>051 L</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>KDS</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>포스맥</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PUL 0697</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AST</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PHA</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LM S</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LM B</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1325,7 +1354,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.0"/>
-    <numFmt numFmtId="180" formatCode="0.000"/>
+    <numFmt numFmtId="177" formatCode="0.000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -1442,7 +1471,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1758,7 +1787,7 @@
     <col min="2" max="2" width="7.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1773,13 +1802,13 @@
         <v>258</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="E1" t="s">
-        <v>281</v>
+        <v>395</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>407</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>414</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1795,11 +1824,11 @@
       <c r="D2">
         <v>0.17219999999999999</v>
       </c>
-      <c r="E2" t="s">
-        <v>260</v>
+      <c r="E2" s="5" t="s">
+        <v>409</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1815,11 +1844,11 @@
       <c r="D3">
         <v>0.19570000000000001</v>
       </c>
-      <c r="E3" t="s">
-        <v>261</v>
+      <c r="E3" s="5" t="s">
+        <v>410</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1857,11 +1886,11 @@
       <c r="D6">
         <v>0.22850000000000001</v>
       </c>
-      <c r="E6" t="s">
-        <v>262</v>
+      <c r="E6" s="5" t="s">
+        <v>408</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1888,11 +1917,11 @@
       <c r="D8">
         <v>0.1361</v>
       </c>
-      <c r="E8" t="s">
-        <v>263</v>
+      <c r="E8" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1905,8 +1934,8 @@
       <c r="C9">
         <v>160</v>
       </c>
-      <c r="E9" t="s">
-        <v>264</v>
+      <c r="E9" s="5" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1919,13 +1948,13 @@
       <c r="C10">
         <v>190</v>
       </c>
-      <c r="E10" t="s">
-        <v>265</v>
+      <c r="E10" s="5" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B11">
         <v>1.5</v>
@@ -1936,7 +1965,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B12">
         <v>1.8</v>
@@ -1947,7 +1976,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B13">
         <v>1.8</v>
@@ -1958,7 +1987,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B14">
         <v>1.8</v>
@@ -1969,7 +1998,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B15">
         <v>1.8</v>
@@ -1980,7 +2009,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B16">
         <v>1.8</v>
@@ -1991,7 +2020,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B17">
         <v>1.8</v>
@@ -2002,16 +2031,16 @@
       <c r="D17">
         <v>0.21099999999999999</v>
       </c>
-      <c r="E17" t="s">
-        <v>267</v>
+      <c r="E17" s="5" t="s">
+        <v>414</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B18">
         <v>1.8</v>
@@ -2022,7 +2051,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B19">
         <v>1.8</v>
@@ -2033,7 +2062,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B20">
         <v>1.8</v>
@@ -2044,16 +2073,16 @@
       <c r="D20">
         <v>0.2359</v>
       </c>
-      <c r="E20" t="s">
-        <v>268</v>
+      <c r="E20" s="5" t="s">
+        <v>415</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B21">
         <v>1.8</v>
@@ -2064,16 +2093,16 @@
       <c r="D21">
         <v>0.24510000000000001</v>
       </c>
-      <c r="E21" t="s">
-        <v>269</v>
+      <c r="E21" s="5" t="s">
+        <v>416</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B22">
         <v>1.8</v>
@@ -2084,7 +2113,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B23">
         <v>1.8</v>
@@ -2095,16 +2124,16 @@
       <c r="D23">
         <v>0.27279999999999999</v>
       </c>
-      <c r="E23" t="s">
-        <v>270</v>
+      <c r="E23" s="5" t="s">
+        <v>417</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -2115,7 +2144,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -2126,7 +2155,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B26">
         <v>2</v>
@@ -2137,16 +2166,16 @@
       <c r="D26">
         <v>0.17219999999999999</v>
       </c>
-      <c r="E26" t="s">
-        <v>271</v>
+      <c r="E26" s="5" t="s">
+        <v>418</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B27">
         <v>2.1</v>
@@ -2157,16 +2186,16 @@
       <c r="D27">
         <v>0.1394</v>
       </c>
-      <c r="E27" t="s">
-        <v>272</v>
+      <c r="E27" s="5" t="s">
+        <v>419</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B28">
         <v>2.1</v>
@@ -2177,16 +2206,16 @@
       <c r="D28">
         <v>0.16059999999999999</v>
       </c>
-      <c r="E28" t="s">
-        <v>273</v>
+      <c r="E28" s="5" t="s">
+        <v>420</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B29">
         <v>2.1</v>
@@ -2197,7 +2226,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B30">
         <v>2.2000000000000002</v>
@@ -2206,12 +2235,12 @@
         <v>170</v>
       </c>
       <c r="E30" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B31">
         <v>2.5</v>
@@ -2222,7 +2251,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B32">
         <v>2.5</v>
@@ -2231,12 +2260,12 @@
         <v>335</v>
       </c>
       <c r="E32" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B33">
         <v>3</v>
@@ -2245,12 +2274,12 @@
         <v>108</v>
       </c>
       <c r="E33" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B34">
         <v>3.6</v>
@@ -2259,12 +2288,12 @@
         <v>589</v>
       </c>
       <c r="E34" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B35">
         <v>4</v>
@@ -2273,12 +2302,12 @@
         <v>108</v>
       </c>
       <c r="E35" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -2287,12 +2316,12 @@
         <v>164</v>
       </c>
       <c r="E36" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B37">
         <v>4</v>
@@ -2303,7 +2332,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="B38">
         <v>4</v>
@@ -2314,7 +2343,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="B39">
         <v>0.3</v>
@@ -2325,7 +2354,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="B40">
         <v>3</v>
@@ -2337,15 +2366,15 @@
         <v>0.25414632000000004</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="B41">
         <v>3</v>
@@ -2357,15 +2386,15 @@
         <v>0.13066704000000001</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="B42">
         <v>3</v>
@@ -2377,15 +2406,15 @@
         <v>0.24888960000000002</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="B43">
         <v>3</v>
@@ -2397,15 +2426,15 @@
         <v>0.22979376000000001</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="B44">
         <v>3</v>
@@ -2417,15 +2446,15 @@
         <v>0.11200032000000001</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="B45">
         <v>0.8</v>
@@ -2436,7 +2465,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="B46">
         <v>2.6</v>
@@ -2445,12 +2474,12 @@
         <v>70.400000000000006</v>
       </c>
       <c r="E46" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="B47">
         <v>2.6</v>
@@ -2461,7 +2490,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="B48">
         <v>2</v>
@@ -2470,9 +2499,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="B49">
         <v>1.6</v>
@@ -2481,9 +2510,9 @@
         <v>234</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="B50">
         <v>0.4</v>
@@ -2492,9 +2521,9 @@
         <v>110</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="B51">
         <v>5</v>
@@ -2502,13 +2531,19 @@
       <c r="C51">
         <v>170</v>
       </c>
+      <c r="D51">
+        <v>0.22689999999999999</v>
+      </c>
       <c r="E51" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="B52">
         <v>5</v>
@@ -2517,9 +2552,9 @@
         <v>172</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="B53">
         <v>5</v>
@@ -2528,9 +2563,9 @@
         <v>306</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="B54">
         <v>5</v>
@@ -2539,9 +2574,9 @@
         <v>402</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B55">
         <v>1.6</v>
@@ -2550,12 +2585,12 @@
         <v>413</v>
       </c>
       <c r="E55" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="B56">
         <v>1.6</v>
@@ -2564,9 +2599,9 @@
         <v>447</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B57">
         <v>1.6</v>
@@ -2575,9 +2610,9 @@
         <v>473</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B58">
         <v>1.6</v>
@@ -2586,12 +2621,12 @@
         <v>520</v>
       </c>
       <c r="E58" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -2600,9 +2635,9 @@
         <v>95</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B60">
         <v>2</v>
@@ -2611,12 +2646,12 @@
         <v>334</v>
       </c>
       <c r="E60" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -2625,12 +2660,12 @@
         <v>500</v>
       </c>
       <c r="E61" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B62">
         <v>2</v>
@@ -2639,12 +2674,12 @@
         <v>503</v>
       </c>
       <c r="E62" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -2653,12 +2688,12 @@
         <v>512</v>
       </c>
       <c r="E63" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B64">
         <v>2</v>
@@ -2669,7 +2704,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B65">
         <v>2</v>
@@ -2680,7 +2715,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B66">
         <v>2</v>
@@ -2689,12 +2724,12 @@
         <v>537</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B67">
         <v>2.2999999999999998</v>
@@ -2703,12 +2738,12 @@
         <v>514</v>
       </c>
       <c r="E67" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B68">
         <v>2.2999999999999998</v>
@@ -2717,12 +2752,12 @@
         <v>520</v>
       </c>
       <c r="E68" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B69">
         <v>2.2999999999999998</v>
@@ -2731,12 +2766,12 @@
         <v>529</v>
       </c>
       <c r="E69" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B70">
         <v>2.6</v>
@@ -2745,12 +2780,12 @@
         <v>160</v>
       </c>
       <c r="E70" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B71">
         <v>2.6</v>
@@ -2759,12 +2794,12 @@
         <v>210</v>
       </c>
       <c r="E71" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B72">
         <v>2.6</v>
@@ -2775,7 +2810,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B73">
         <v>2.6</v>
@@ -2784,12 +2819,12 @@
         <v>495</v>
       </c>
       <c r="E73" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B74">
         <v>2.6</v>
@@ -2800,7 +2835,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B75">
         <v>2.6</v>
@@ -2811,7 +2846,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B76">
         <v>2.8</v>
@@ -2820,12 +2855,12 @@
         <v>392</v>
       </c>
       <c r="E76" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B77">
         <v>2.8</v>
@@ -2834,12 +2869,12 @@
         <v>641</v>
       </c>
       <c r="E77" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B78">
         <v>2.8</v>
@@ -2850,7 +2885,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B79">
         <v>3</v>
@@ -2859,12 +2894,12 @@
         <v>195</v>
       </c>
       <c r="E79" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B80">
         <v>3</v>
@@ -2873,12 +2908,12 @@
         <v>525</v>
       </c>
       <c r="E80" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B81">
         <v>3.2</v>
@@ -2887,12 +2922,12 @@
         <v>106</v>
       </c>
       <c r="E81" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B82">
         <v>3.2</v>
@@ -2901,12 +2936,12 @@
         <v>514</v>
       </c>
       <c r="E82" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B83">
         <v>4</v>
@@ -2915,12 +2950,12 @@
         <v>153</v>
       </c>
       <c r="E83" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B84">
         <v>4</v>
@@ -2931,7 +2966,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B85">
         <v>4</v>
@@ -2942,7 +2977,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B86">
         <v>4</v>
@@ -2953,7 +2988,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B87">
         <v>4</v>
@@ -2962,12 +2997,12 @@
         <v>382</v>
       </c>
       <c r="E87" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B88">
         <v>4</v>
@@ -2976,12 +3011,12 @@
         <v>585</v>
       </c>
       <c r="E88" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B89">
         <v>4</v>
@@ -2992,7 +3027,7 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B90">
         <v>5</v>
@@ -3001,12 +3036,12 @@
         <v>590</v>
       </c>
       <c r="E90" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B91">
         <v>5</v>
@@ -3015,12 +3050,12 @@
         <v>602</v>
       </c>
       <c r="E91" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B92">
         <v>5.5</v>
@@ -3029,12 +3064,12 @@
         <v>654</v>
       </c>
       <c r="E92" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -3045,7 +3080,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="B94">
         <v>2</v>
@@ -3056,7 +3091,7 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="B95">
         <v>0.4</v>
@@ -3067,7 +3102,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="B96">
         <v>0.5</v>
@@ -3078,7 +3113,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="B97">
         <v>0.8</v>
@@ -3089,7 +3124,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="B98">
         <v>2</v>
@@ -3100,7 +3135,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="B99">
         <v>2.2999999999999998</v>
@@ -3109,12 +3144,12 @@
         <v>508</v>
       </c>
       <c r="E99" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="B100">
         <v>2.2999999999999998</v>
@@ -3123,12 +3158,12 @@
         <v>530</v>
       </c>
       <c r="E100" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="B101">
         <v>2.6</v>
@@ -3137,12 +3172,12 @@
         <v>508</v>
       </c>
       <c r="E101" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="B102">
         <v>0.75</v>
@@ -3151,12 +3186,12 @@
         <v>96</v>
       </c>
       <c r="E102" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="B103">
         <v>4</v>
@@ -3165,12 +3200,12 @@
         <v>186</v>
       </c>
       <c r="E103" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="B104">
         <v>4</v>
@@ -3179,12 +3214,12 @@
         <v>1230</v>
       </c>
       <c r="E104" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="B105">
         <v>5</v>
@@ -3195,7 +3230,7 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B106">
         <v>0.5</v>
@@ -3206,7 +3241,7 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B107">
         <v>0.5</v>
@@ -3217,7 +3252,7 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B108">
         <v>0.5</v>
@@ -3228,7 +3263,7 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B109">
         <v>0.6</v>
@@ -3239,7 +3274,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B110">
         <v>0.6</v>
@@ -3250,7 +3285,7 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -3261,7 +3296,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -3272,7 +3307,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -3283,7 +3318,7 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B114">
         <v>1.2</v>
@@ -3292,12 +3327,12 @@
         <v>65</v>
       </c>
       <c r="E114" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B115">
         <v>1.2</v>
@@ -3306,12 +3341,12 @@
         <v>165</v>
       </c>
       <c r="E115" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B116">
         <v>1.2</v>
@@ -3320,12 +3355,12 @@
         <v>184</v>
       </c>
       <c r="E116" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B117">
         <v>1.4</v>
@@ -3336,7 +3371,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B118">
         <v>1.4</v>
@@ -3347,7 +3382,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B119">
         <v>1.4</v>
@@ -3358,7 +3393,7 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B120">
         <v>1.5</v>
@@ -3369,7 +3404,7 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B121">
         <v>1.5</v>
@@ -3380,7 +3415,7 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B122">
         <v>1.6</v>
@@ -3391,7 +3426,7 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B123">
         <v>1.6</v>
@@ -3400,12 +3435,12 @@
         <v>336</v>
       </c>
       <c r="E123" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B124">
         <v>2</v>
@@ -3416,7 +3451,7 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B125">
         <v>2</v>
@@ -3427,7 +3462,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B126">
         <v>2</v>
@@ -3436,12 +3471,12 @@
         <v>69</v>
       </c>
       <c r="E126" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B127">
         <v>2</v>
@@ -3450,12 +3485,12 @@
         <v>117</v>
       </c>
       <c r="E127" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B128">
         <v>2.2999999999999998</v>
@@ -3464,12 +3499,12 @@
         <v>1219</v>
       </c>
       <c r="E128" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B129">
         <v>2.6</v>
@@ -3480,7 +3515,7 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B130">
         <v>3</v>
@@ -3489,12 +3524,12 @@
         <v>48</v>
       </c>
       <c r="E130" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B131">
         <v>3</v>
@@ -3503,12 +3538,12 @@
         <v>52</v>
       </c>
       <c r="E131" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="B132">
         <v>2.2999999999999998</v>
@@ -3519,7 +3554,7 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="B133">
         <v>2.6</v>
@@ -3531,15 +3566,15 @@
         <v>0.38669999999999999</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="B134">
         <v>2.2999999999999998</v>
@@ -3550,7 +3585,7 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="B135">
         <v>2.2999999999999998</v>
@@ -3561,7 +3596,7 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="B136">
         <v>1.6</v>
@@ -3572,7 +3607,7 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="B137">
         <v>2</v>
@@ -3583,7 +3618,7 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="B138">
         <v>2</v>
@@ -3592,12 +3627,12 @@
         <v>113</v>
       </c>
       <c r="E138" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="B139">
         <v>2</v>
@@ -3606,12 +3641,12 @@
         <v>123</v>
       </c>
       <c r="E139" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="B140">
         <v>2</v>
@@ -3620,12 +3655,12 @@
         <v>131</v>
       </c>
       <c r="E140" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="B141">
         <v>2</v>
@@ -3634,12 +3669,12 @@
         <v>180</v>
       </c>
       <c r="E141" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="B142">
         <v>2.2999999999999998</v>
@@ -3648,12 +3683,12 @@
         <v>223.5</v>
       </c>
       <c r="E142" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="B143">
         <v>4</v>
@@ -3662,12 +3697,12 @@
         <v>59</v>
       </c>
       <c r="E143" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="B144">
         <v>4</v>
@@ -3678,7 +3713,7 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="B145">
         <v>4</v>
@@ -3687,12 +3722,12 @@
         <v>164</v>
       </c>
       <c r="E145" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="B146">
         <v>4</v>
@@ -3701,12 +3736,12 @@
         <v>202</v>
       </c>
       <c r="E146" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B147">
         <v>1.6</v>
@@ -3717,7 +3752,7 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B148">
         <v>1.6</v>
@@ -3726,12 +3761,12 @@
         <v>324</v>
       </c>
       <c r="E148" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B149">
         <v>1.6</v>
@@ -3740,12 +3775,12 @@
         <v>336</v>
       </c>
       <c r="E149" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B150">
         <v>1.8</v>
@@ -3754,12 +3789,12 @@
         <v>536</v>
       </c>
       <c r="E150" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B151">
         <v>1.8</v>
@@ -3769,13 +3804,13 @@
       </c>
       <c r="D151" s="5"/>
       <c r="E151" s="5" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="F151" s="5"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B152">
         <v>1.8</v>
@@ -3784,12 +3819,12 @@
         <v>581</v>
       </c>
       <c r="E152" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B153">
         <v>2</v>
@@ -3800,7 +3835,7 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B154">
         <v>2</v>
@@ -3809,12 +3844,12 @@
         <v>305</v>
       </c>
       <c r="E154" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B155">
         <v>2</v>
@@ -3823,12 +3858,12 @@
         <v>550</v>
       </c>
       <c r="E155" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B156">
         <v>2.2999999999999998</v>
@@ -3837,12 +3872,12 @@
         <v>540</v>
       </c>
       <c r="E156" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B157">
         <v>2.6</v>
@@ -3853,7 +3888,7 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B158">
         <v>2.6</v>
@@ -3862,12 +3897,12 @@
         <v>120</v>
       </c>
       <c r="E158" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B159">
         <v>3</v>
@@ -3878,7 +3913,7 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B160">
         <v>3</v>
@@ -3887,12 +3922,12 @@
         <v>230</v>
       </c>
       <c r="E160" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B161">
         <v>3.6</v>
@@ -3901,9 +3936,9 @@
         <v>64</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B162">
         <v>3.6</v>
@@ -3911,13 +3946,19 @@
       <c r="C162">
         <v>118</v>
       </c>
+      <c r="D162">
+        <v>0.11840000000000001</v>
+      </c>
       <c r="E162" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+        <v>345</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B163">
         <v>3.6</v>
@@ -3926,9 +3967,9 @@
         <v>120</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B164">
         <v>3.6</v>
@@ -3937,9 +3978,9 @@
         <v>124</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B165">
         <v>3.6</v>
@@ -3948,9 +3989,9 @@
         <v>143</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B166">
         <v>3.6</v>
@@ -3958,13 +3999,19 @@
       <c r="C166">
         <v>150</v>
       </c>
-      <c r="E166" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D166">
+        <v>0.22470000000000001</v>
+      </c>
+      <c r="E166" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B167">
         <v>4</v>
@@ -3973,9 +4020,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B168">
         <v>4.5</v>
@@ -3984,12 +4031,12 @@
         <v>170</v>
       </c>
       <c r="E168" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B169">
         <v>4.5</v>
@@ -3998,12 +4045,12 @@
         <v>175</v>
       </c>
       <c r="E169" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B170">
         <v>5</v>
@@ -4012,9 +4059,9 @@
         <v>170</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B171">
         <v>5</v>
@@ -4023,12 +4070,12 @@
         <v>680</v>
       </c>
       <c r="E171" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="B172">
         <v>1.8</v>
@@ -4037,9 +4084,9 @@
         <v>74</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="B173">
         <v>1.8</v>
@@ -4048,12 +4095,12 @@
         <v>335</v>
       </c>
       <c r="E173" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="B174">
         <v>0.5</v>
@@ -4062,12 +4109,12 @@
         <v>156</v>
       </c>
       <c r="E174" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="B175">
         <v>2</v>
@@ -4076,9 +4123,9 @@
         <v>315</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="B176">
         <v>2</v>
@@ -4089,7 +4136,7 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="B177">
         <v>2.5</v>
@@ -4098,12 +4145,12 @@
         <v>1219</v>
       </c>
       <c r="E177" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -4114,7 +4161,7 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -4125,7 +4172,7 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="B180">
         <v>0.6</v>
@@ -4134,12 +4181,12 @@
         <v>60</v>
       </c>
       <c r="E180" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="B181">
         <v>3</v>
@@ -4148,12 +4195,12 @@
         <v>168</v>
       </c>
       <c r="E181" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="B182">
         <v>3</v>
@@ -4162,12 +4209,12 @@
         <v>1000</v>
       </c>
       <c r="E182" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="B183">
         <v>6</v>
@@ -4176,12 +4223,12 @@
         <v>1000</v>
       </c>
       <c r="E183" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="B184">
         <v>0.6</v>
@@ -4192,7 +4239,7 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -4203,7 +4250,7 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="B186">
         <v>1.5</v>
@@ -4214,7 +4261,7 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="B187">
         <v>1.5</v>
@@ -4223,12 +4270,12 @@
         <v>68</v>
       </c>
       <c r="E187" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="B188">
         <v>2</v>
@@ -4237,12 +4284,12 @@
         <v>50</v>
       </c>
       <c r="E188" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="B189">
         <v>2</v>
@@ -4251,12 +4298,12 @@
         <v>81</v>
       </c>
       <c r="E189" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="B190">
         <v>2</v>
@@ -4267,7 +4314,7 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="B191">
         <v>2</v>
@@ -4278,7 +4325,7 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="B192">
         <v>2</v>
@@ -4287,9 +4334,9 @@
         <v>126</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="B193">
         <v>2</v>
@@ -4298,9 +4345,9 @@
         <v>154</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="B194">
         <v>2</v>
@@ -4309,12 +4356,12 @@
         <v>180</v>
       </c>
       <c r="E194" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="B195">
         <v>0.8</v>
@@ -4323,12 +4370,12 @@
         <v>48</v>
       </c>
       <c r="E195" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -4337,9 +4384,9 @@
         <v>92</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -4348,9 +4395,9 @@
         <v>156</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="B198">
         <v>1.7</v>
@@ -4359,9 +4406,9 @@
         <v>330</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="B199">
         <v>1.8</v>
@@ -4372,112 +4419,121 @@
       <c r="D199">
         <v>0.19170000000000001</v>
       </c>
-      <c r="E199" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E199" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="F199" s="5" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="B200" s="6">
         <v>5.9</v>
       </c>
       <c r="E200" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="B201" s="6">
         <v>6</v>
       </c>
       <c r="E201" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="B202" s="6">
         <v>6.9</v>
       </c>
       <c r="E202" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="B203" s="6">
         <v>7</v>
       </c>
-      <c r="E203" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D203">
+        <v>2.6700000000000002E-2</v>
+      </c>
+      <c r="E203" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="F203" s="5" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="B204" s="6">
         <v>7.35</v>
       </c>
       <c r="E204" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="B205" s="6">
         <v>7.45</v>
       </c>
       <c r="E205" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="B206" s="6">
         <v>8</v>
       </c>
       <c r="E206" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="B207" s="6">
         <v>6</v>
       </c>
       <c r="E207" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="B208" s="6">
         <v>7.35</v>
       </c>
       <c r="E208" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="B209" s="6">
         <v>7.9</v>
@@ -4485,7 +4541,7 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="B210" s="6">
         <v>7.25</v>
@@ -4493,7 +4549,7 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="B211" s="6">
         <v>6.4</v>
@@ -4501,7 +4557,7 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="B212" s="6">
         <v>6</v>
@@ -4509,7 +4565,7 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="5" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="B213" s="6">
         <v>5</v>
@@ -4521,15 +4577,15 @@
         <v>4.2050000000000001</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="F213" s="5" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="5" t="s">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="B214" s="6">
         <v>4.5</v>
@@ -4541,15 +4597,15 @@
         <v>0.505</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="F214" s="5" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="5" t="s">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="B215" s="6">
         <v>4.5</v>
@@ -4561,10 +4617,10 @@
         <v>1.93</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="F215" s="5" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
